--- a/review/abilities/workbooks/13_Ancestry_Human.xlsx
+++ b/review/abilities/workbooks/13_Ancestry_Human.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Traits" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Pairs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Compare" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Change Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traits" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pairs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compare" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Traits'!$A$4:$L$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Traits'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pairs'!$A$4:$G$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Pairs'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Change Log'!$A$4:$R$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Change Log'!$A$4:$Q$204</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Change Log'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Change Log'!$A$1:$R$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Change Log'!$A$1:$Q$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -82,7 +82,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="007F6000"/>
+      <color rgb="00006100"/>
       <sz val="9"/>
     </font>
     <font>
@@ -116,7 +116,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -188,7 +188,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -225,19 +225,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <b val="1"/>
-        <color rgb="001F3864"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D9E1F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -730,7 +717,7 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Adaptable, social and travel-minded. Human has HP +2, Speed 6, and traits for speed/travel, languages, risky noncombat luck, hospitality and toughness. The ancestry is the most flexible at character creation.</t>
+          <t>Adaptable, social and travel-minded. Human has HP +2, Speed 6, and traits for adaptability, borrowed ancestry traits, risky noncombat luck, ingenuity and toughness. The ancestry is the most flexible at character creation.</t>
         </is>
       </c>
     </row>
@@ -744,7 +731,7 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Can choose HP or Speed; A Foot in Two Worlds and Make Room at the Fire give strong social tools; The Impossible Streak is a broad noncombat Boon. The ancestry fits almost any class.</t>
+          <t>Never Quite Finished adds HP and death-mark resilience; Adaptable adds +1 DP per level; A Foot in Two Worlds gives cross-ancestry flexibility; Ingenuity gives a creative tool answer; The Impossible Streak is a broad noncombat Boon. The ancestry fits almost any class.</t>
         </is>
       </c>
     </row>
@@ -758,7 +745,7 @@
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Never Quite Finished and Road in the Blood duplicate Dwarf/Elf stat traits. The travel clause on Road is mostly flavor because there is no exhaustion rule. The Impossible Streak may overshadow skill-focused classes.</t>
+          <t>Adaptable is a strong character-building advantage rather than a scene ability. The Impossible Streak may overshadow skill-focused classes.</t>
         </is>
       </c>
     </row>
@@ -772,7 +759,7 @@
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Give each stat trait a Human-specific rider (travel/endurance for Speed; a last-stand clause for HP). Clarify what 'the difficult way' means for The Impossible Streak. Keep the flexibility; it is the ancestry's identity.</t>
+          <t>Adaptable and Never Quite Finished are approved. Clarify what 'the difficult way' means for The Impossible Streak. Keep the flexibility; it is the ancestry's identity.</t>
         </is>
       </c>
     </row>
@@ -818,7 +805,7 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Stubborn as Bedrock</t>
+          <t>Hard as Bedrock</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -867,7 +854,7 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Combat, Defense, Exploration, Social, Support, Utility</t>
+          <t>Combat, Defense, Exploration, Social, Utility</t>
         </is>
       </c>
     </row>
@@ -884,12 +871,12 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Never Quite Finished, Road in the Blood</t>
+          <t>Never Quite Finished</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Defense, Exploration, Movement, Social, Support, Utility</t>
+          <t>Defense, Exploration, Social, Utility</t>
         </is>
       </c>
     </row>
@@ -930,17 +917,17 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Two pairs of ancestry traits are mechanically identical: Stubborn as Bedrock and Never Quite Finished are both '+1 maximum HP'; Grace of the Elder Folk and Road in the Blood are both '+1 base Speed'.</t>
+          <t>The baseline duplicate stat traits have been differentiated: Hard as Bedrock (+1 maximum HP), Never Quite Finished (+1 maximum HP and a death-mark Boon), Grace of the Elder Folk (+1 Speed) and Adaptable (+1 DP per level).</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Keep the stat but add a small ancestry-specific rider: Dwarf +1 to stabilization or reduce Bleeding after a rest; Human a travel/endurance clause; Elf ignore 1 square of difficult terrain once per scene; Human speed a forced-march benefit.</t>
+          <t>No further action; keep the differentiation.</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1154,12 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Maximum HP +1. Describe the ordinary hardship that taught you to keep going.</t>
+          <t>Maximum HP +1 and 1 Boon to Fortitude rolls to resist death marks. Describe the ordinary hardship that taught you to keep going.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Maximum HP +1. Describe the ordinary hardship that taught you to keep going.</t>
+          <t>Maximum HP +1. You gain 1 Boon to Fortitude rolls to resist death marks. Describe the ordinary hardship that taught you to keep going.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -1187,12 +1174,12 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Simple durability with a strong character prompt. It is mechanically identical to Dwarf Stubborn as Bedrock.</t>
+          <t>Simple durability plus death-mark resilience. It is now distinct from Dwarf Hard as Bedrock: Dwarf is raw HP, Human is stubborn survival.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Add a Human-specific rider: once per day, when you would be knocked prone or reduced to 0 HP, describe the hardship and gain 1 Boon to the relevant defense. Keep the +1 HP.</t>
+          <t>Approved: +1 maximum HP and 1 Boon to Fortitude rolls to resist death marks.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr"/>
@@ -1203,13 +1190,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="54" customHeight="1">
+    <row r="6" ht="41.5" customHeight="1">
       <c r="A6" s="8" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Road in the Blood</t>
+          <t>Adaptable</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -1219,17 +1206,17 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Base Speed +1. Long journeys remain ordinary travel; no exhaustion rule.</t>
+          <t>Gain 1 additional DP at each level, including level 0.</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Base Speed +1. Long journeys remain ordinary travel; this creates no exhaustion rule.</t>
+          <t>You gain 1 additional DP at each level, including level 0.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Movement, Exploration</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1239,12 +1226,12 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Simple and strong; the travel clause is mostly flavor because the system has no exhaustion rule.</t>
+          <t>Strong flexibility trait: one extra DP every level. It is a character-building advantage rather than a scene ability.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Differentiate from Elf Grace with a travel-specific benefit: +1 to forced-march checks, or ignore 1 point of travel-related Bane. Otherwise the two traits are the same pick.</t>
+          <t>Approved: replaced Road in the Blood with Adaptable; +1 additional DP at each level, including level 0.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr"/>
@@ -1271,12 +1258,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Know two additional ordinary spoken languages; choose the communities that taught you. Does not grant a second culture's discipline or card.</t>
+          <t>Choose another ancestry; learn one native language and gain one trait from its list as this trait’s benefit. Keep Human base HP and Speed.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Know two additional ordinary spoken [languages](../rules/languages.md). Choose the communities that taught you; this does not grant a second culture’s discipline or card.</t>
+          <t>Choose another ancestry. You learn one language native to that ancestry and gain one trait from that ancestry’s trait list as this trait’s benefit. You keep your Human base HP and Speed.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1291,12 +1278,12 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Strong utility if languages matter; compare to Another Tongue (1 DP for one language). It also gives the Human a cosmopolitan story.</t>
+          <t>Cross-ancestry flexibility: the Human can borrow one trait from another ancestry while keeping Human base values. Strong character-building choice.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Add a small cultural read (1 Boon to etiquette or gathering information in those communities) so it is not only a language list. Clarify whether sign languages count.</t>
+          <t>Approved: replaced the language-only benefit with one native language plus one trait from another ancestry.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr"/>
@@ -1313,7 +1300,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Make Room at the Fire</t>
+          <t>Ingenuity</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -1323,17 +1310,17 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Once per scene, when you offer genuine food, shelter or shared work to a nonhostile person, gain 1 Boon to the next Guile roll seeking ordinary hospitality or trust from them before the scene ends.</t>
+          <t>Once per scene, assemble a temporary tool, implement or weapon from nearby materials. Gain 1 Boon to the next roll using it; it lasts until the end of the scene.</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Once per scene, when you offer genuine food, shelter or shared work to a nonhostile person, gain 1 Boon to the next Guile roll seeking ordinary hospitality or trust from them before the scene ends. No automatic friendship or compelled response.</t>
+          <t>Once per scene, you can assemble a temporary tool, implement or weapon from nearby materials. Gain 1 Boon to the next roll you make using it. The tool lasts until the end of the scene.</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Social, Support</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1343,12 +1330,12 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Excellent social trait with a concrete trigger and a clear limit. It rewards roleplay and gives the Human a community-building niche.</t>
+          <t>Human ingenuity: broad, creative and useful in combat, exploration and social scenes. The DA adjudicates what the materials can become.</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Clarify what counts as 'genuine' and whether the Boon can apply to a group check. Good as written otherwise.</t>
+          <t>Approved: replaced Make Room at the Fire with Ingenuity; once per scene, build a temporary tool/implement/weapon for 1 Boon.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr"/>
@@ -1359,7 +1346,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="66.5" customHeight="1">
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="7" t="n">
         <v>5</v>
       </c>
@@ -1375,12 +1362,12 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Once per day, declare before an ordinary noncombat roll that you are taking the difficult way; gain 1 Boon. Still need a plausible method and specialist permission; does not change a card's attribute.</t>
+          <t>Once per day, before an ordinary noncombat roll, describe the difficult way you are taking; gain 3 Boons to that roll.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Once per day, declare before an ordinary noncombat roll that you are taking the difficult way on purpose. Gain 1 Boon. You still need a plausible method and any specialist permission; this does not change a card’s attribute.</t>
+          <t>Once per day, before an ordinary noncombat roll, describe the difficult way you are taking. Gain 3 Boons to that roll.</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1395,12 +1382,12 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Strong skill trait and a great Human story beat. It is broader than most noncombat traits because it applies to any ordinary noncombat roll.</t>
+          <t>Strong once-per-day noncombat moment: 3 Boons on a difficult approach. It is narrower than Halfling A Little Luck because it only applies to noncombat rolls.</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Clarify what makes an approach 'the difficult way' and whether it can apply to a group roll. Monitor if it overshadows skill-focused classes.</t>
+          <t>Approved: once per day, 3 Boons on an ordinary noncombat roll using a described difficult approach.</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr"/>
@@ -1428,15 +1415,12 @@
       <formula>J5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>J5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>J5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="J5:J9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1527,22 +1511,22 @@
     <row r="5" ht="41.5" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Never Quite Finished + Road in the Blood</t>
+          <t>Never Quite Finished + Adaptable</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Defense, Movement, Exploration</t>
+          <t>Defense, Utility</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Durable scout</t>
+          <t>Practical fighter</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Never Quite Finished leans defense; Road in the Blood leans movement, exploration. Together they cover defense, movement, exploration.</t>
+          <t>Never Quite Finished leans defense; Adaptable leans utility. Together they cover defense, utility.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -1585,22 +1569,22 @@
     <row r="7" ht="41.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Never Quite Finished + Make Room at the Fire</t>
+          <t>Never Quite Finished + Ingenuity</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Defense, Social, Support</t>
+          <t>Defense, Utility</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Protective support</t>
+          <t>Practical fighter</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Never Quite Finished leans defense; Make Room at the Fire leans social, support. Together they cover defense, social, support.</t>
+          <t>Never Quite Finished leans defense; Ingenuity leans utility. Together they cover defense, utility.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1643,56 +1627,56 @@
     <row r="9" ht="41.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Road in the Blood + A Foot in Two Worlds</t>
+          <t>Adaptable + A Foot in Two Worlds</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Movement, Exploration, Social, Utility</t>
+          <t>Social, Utility</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Scout / guide</t>
+          <t>Skill specialist</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Road in the Blood leans movement, exploration; A Foot in Two Worlds leans social, utility. Together they cover movement, exploration, social, utility.</t>
+          <t>Adaptable leans utility; A Foot in Two Worlds leans social, utility. Together they cover social, utility.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Strong out-of-combat pair; check that the character still has a combat contribution.</t>
+          <t>Both traits are campaign-dependent. Confirm the campaign will feature the relevant terrain, craft or social scenes.</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
     </row>
-    <row r="10" ht="41.5" customHeight="1">
+    <row r="10" ht="29" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Road in the Blood + Make Room at the Fire</t>
+          <t>Adaptable + Ingenuity</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Movement, Exploration, Social, Support</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Scout / guide</t>
+          <t>Skill specialist</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Road in the Blood leans movement, exploration; Make Room at the Fire leans social, support. Together they cover movement, exploration, social, support.</t>
+          <t>Adaptable leans utility; Ingenuity leans utility. Together they cover utility.</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Strong out-of-combat pair; check that the character still has a combat contribution.</t>
+          <t>Both traits point at the same pillar. Strong specialization; make sure the character has an answer outside it.</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr"/>
@@ -1701,27 +1685,27 @@
     <row r="11" ht="41.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Road in the Blood + The Impossible Streak</t>
+          <t>Adaptable + The Impossible Streak</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Movement, Exploration, Social, Utility</t>
+          <t>Exploration, Social, Utility</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Scout / guide</t>
+          <t>Guide and envoy</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Road in the Blood leans movement, exploration; The Impossible Streak leans utility, social, exploration. Together they cover movement, exploration, social, utility.</t>
+          <t>Adaptable leans utility; The Impossible Streak leans utility, social, exploration. Together they cover exploration, social, utility.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Strong out-of-combat pair; check that the character still has a combat contribution.</t>
+          <t>Both traits are campaign-dependent. Confirm the campaign will feature the relevant terrain, craft or social scenes.</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
@@ -1730,22 +1714,22 @@
     <row r="12" ht="41.5" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>A Foot in Two Worlds + Make Room at the Fire</t>
+          <t>A Foot in Two Worlds + Ingenuity</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Social, Support, Utility</t>
+          <t>Social, Utility</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Diplomat-support</t>
+          <t>Skill specialist</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>A Foot in Two Worlds leans social, utility; Make Room at the Fire leans social, support. Together they cover social, support, utility.</t>
+          <t>A Foot in Two Worlds leans social, utility; Ingenuity leans utility. Together they cover social, utility.</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -1788,12 +1772,12 @@
     <row r="14" ht="41.5" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Make Room at the Fire + The Impossible Streak</t>
+          <t>Ingenuity + The Impossible Streak</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Exploration, Social, Support, Utility</t>
+          <t>Exploration, Social, Utility</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1803,7 +1787,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Make Room at the Fire leans social, support; The Impossible Streak leans utility, social, exploration. Together they cover exploration, social, support, utility.</t>
+          <t>Ingenuity leans utility; The Impossible Streak leans utility, social, exploration. Together they cover exploration, social, utility.</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -1831,15 +1815,12 @@
       <formula>F5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>F5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>F5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="F5:F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1956,7 +1937,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Stubborn as Bedrock</t>
+          <t>Hard as Bedrock</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -2045,7 +2026,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Combat, Defense, Exploration, Social, Support, Utility</t>
+          <t>Combat, Defense, Exploration, Social, Utility</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -2082,12 +2063,12 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Never Quite Finished, Road in the Blood</t>
+          <t>Never Quite Finished</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Defense, Exploration, Movement, Social, Support, Utility</t>
+          <t>Defense, Exploration, Social, Utility</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -2118,7 +2099,7 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>• Stubborn as Bedrock and Never Quite Finished are both '+1 maximum HP'; Grace of the Elder Folk and Road in the Blood are both '+1 base Speed'. The mechanics are identical; only the fiction differs (F12).</t>
+          <t>• Hard as Bedrock and Never Quite Finished are both '+1 maximum HP'; Grace of the Elder Folk and Road in the Blood are both '+1 base Speed'. The mechanics are identical; only the fiction differs (F12).</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2182,12 +2163,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" style="11" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" style="11" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2268,30 +2248,25 @@
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Playtest status</t>
+          <t>Book issue</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>Book issue</t>
+          <t>Foundry issue</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Foundry issue</t>
+          <t>Commit SHA</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Commit SHA</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2315,7 +2290,6 @@
       <c r="O5" s="7" t="inlineStr"/>
       <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="7" t="inlineStr"/>
-      <c r="R5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr"/>
@@ -2335,7 +2309,6 @@
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr"/>
@@ -2355,7 +2328,6 @@
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr"/>
       <c r="Q7" s="7" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="8" t="inlineStr"/>
@@ -2375,7 +2347,6 @@
       <c r="O8" s="8" t="inlineStr"/>
       <c r="P8" s="8" t="inlineStr"/>
       <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="8" t="inlineStr"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr"/>
@@ -2395,7 +2366,6 @@
       <c r="O9" s="7" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr"/>
       <c r="Q9" s="7" t="inlineStr"/>
-      <c r="R9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="8" t="inlineStr"/>
@@ -2415,7 +2385,6 @@
       <c r="O10" s="8" t="inlineStr"/>
       <c r="P10" s="8" t="inlineStr"/>
       <c r="Q10" s="8" t="inlineStr"/>
-      <c r="R10" s="8" t="inlineStr"/>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr"/>
@@ -2435,7 +2404,6 @@
       <c r="O11" s="7" t="inlineStr"/>
       <c r="P11" s="7" t="inlineStr"/>
       <c r="Q11" s="7" t="inlineStr"/>
-      <c r="R11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="16.5" customHeight="1">
       <c r="A12" s="8" t="inlineStr"/>
@@ -2455,7 +2423,6 @@
       <c r="O12" s="8" t="inlineStr"/>
       <c r="P12" s="8" t="inlineStr"/>
       <c r="Q12" s="8" t="inlineStr"/>
-      <c r="R12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr"/>
@@ -2475,7 +2442,6 @@
       <c r="O13" s="7" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr"/>
       <c r="Q13" s="7" t="inlineStr"/>
-      <c r="R13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="8" t="inlineStr"/>
@@ -2495,7 +2461,6 @@
       <c r="O14" s="8" t="inlineStr"/>
       <c r="P14" s="8" t="inlineStr"/>
       <c r="Q14" s="8" t="inlineStr"/>
-      <c r="R14" s="8" t="inlineStr"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr"/>
@@ -2515,7 +2480,6 @@
       <c r="O15" s="7" t="inlineStr"/>
       <c r="P15" s="7" t="inlineStr"/>
       <c r="Q15" s="7" t="inlineStr"/>
-      <c r="R15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="8" t="inlineStr"/>
@@ -2535,23 +2499,19 @@
       <c r="O16" s="8" t="inlineStr"/>
       <c r="P16" s="8" t="inlineStr"/>
       <c r="Q16" s="8" t="inlineStr"/>
-      <c r="R16" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R204"/>
+  <autoFilter ref="A4:Q204"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation sqref="I5:I204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Change type" error="Choose one of: Editorial, Wording, Mechanical, Rename, Add, Remove, Tier / DP, ID migration" promptTitle="Change type" prompt="Classify the change." type="list">
       <formula1>"Editorial,Wording,Mechanical,Rename,Add,Remove,Tier / DP,ID migration"</formula1>
     </dataValidation>
     <dataValidation sqref="K5:K204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose one of: Proposed, Approved, Rejected, Deferred" promptTitle="Decision" prompt="Approval state for this change." type="list">
       <formula1>"Proposed,Approved,Rejected,Deferred"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M5:M204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Playtest status" error="Choose one of: Not needed, Pending, Passed, Failed, N/A" promptTitle="Playtest status" prompt="Playtest evidence for mechanical changes." type="list">
-      <formula1>"Not needed,Pending,Passed,Failed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
